--- a/ontwikkeling/vri-5.1/symbolen-concept-5.1.xlsx
+++ b/ontwikkeling/vri-5.1/symbolen-concept-5.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingcrow-my.sharepoint.com/personal/elisabeth_devries_crow_nl/Documents/Documents/GitHub/NLCS/ontwikkeling/vri-5.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingcrow-my.sharepoint.com/personal/elisabeth_devries_crow_nl/Documents/Documents/GitHub/NLCSdev/ontwikkeling/vri-5.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:9_{692B770C-9336-4EE2-BD00-50B8B4754DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8293F555-25F7-474A-9FD6-3FB298DD60DF}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="13_ncr:9_{692B770C-9336-4EE2-BD00-50B8B4754DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E591EB3-2F7B-4EF0-B751-C55EFE704A7A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F86B7F22-60E8-4818-B9D8-E9B948E6A380}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F86B7F22-60E8-4818-B9D8-E9B948E6A380}"/>
   </bookViews>
   <sheets>
     <sheet name="symbolen-concept-5.1" sheetId="1" r:id="rId1"/>
@@ -5152,16 +5152,7 @@
     <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5491,7 +5482,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51E2713C-FA2A-4405-8F21-738B3A046828}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S1118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5527,7 +5517,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>767</v>
       </c>
@@ -5561,7 +5551,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>831</v>
       </c>
@@ -5595,7 +5585,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -5629,7 +5619,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>207</v>
       </c>
@@ -5663,7 +5653,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>377</v>
       </c>
@@ -5697,7 +5687,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>539</v>
       </c>
@@ -5731,7 +5721,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>541</v>
       </c>
@@ -5765,7 +5755,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>829</v>
       </c>
@@ -5799,7 +5789,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>309</v>
       </c>
@@ -5833,7 +5823,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>311</v>
       </c>
@@ -5867,7 +5857,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>81</v>
       </c>
@@ -5901,7 +5891,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>565</v>
       </c>
@@ -5935,7 +5925,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>215</v>
       </c>
@@ -5969,7 +5959,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>669</v>
       </c>
@@ -6003,7 +5993,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>285</v>
       </c>
@@ -6037,7 +6027,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>189</v>
       </c>
@@ -6071,7 +6061,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>689</v>
       </c>
@@ -6105,7 +6095,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>643</v>
       </c>
@@ -6139,7 +6129,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>865</v>
       </c>
@@ -6173,7 +6163,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>867</v>
       </c>
@@ -6207,7 +6197,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>861</v>
       </c>
@@ -6241,7 +6231,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>855</v>
       </c>
@@ -6275,7 +6265,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>877</v>
       </c>
@@ -6309,7 +6299,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>883</v>
       </c>
@@ -6343,7 +6333,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -6377,7 +6367,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>343</v>
       </c>
@@ -6411,7 +6401,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>441</v>
       </c>
@@ -6445,7 +6435,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>791</v>
       </c>
@@ -6479,7 +6469,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>365</v>
       </c>
@@ -6513,7 +6503,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>475</v>
       </c>
@@ -6547,7 +6537,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>639</v>
       </c>
@@ -6581,7 +6571,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>423</v>
       </c>
@@ -6615,7 +6605,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>853</v>
       </c>
@@ -6649,7 +6639,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>543</v>
       </c>
@@ -6683,7 +6673,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>385</v>
       </c>
@@ -6717,7 +6707,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>157</v>
       </c>
@@ -6751,7 +6741,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>637</v>
       </c>
@@ -6785,7 +6775,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -6819,7 +6809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -6853,7 +6843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>303</v>
       </c>
@@ -6887,7 +6877,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -6921,7 +6911,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>201</v>
       </c>
@@ -6955,7 +6945,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>835</v>
       </c>
@@ -6989,7 +6979,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>217</v>
       </c>
@@ -7023,7 +7013,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>827</v>
       </c>
@@ -7057,7 +7047,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>819</v>
       </c>
@@ -7091,7 +7081,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>375</v>
       </c>
@@ -7125,7 +7115,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>485</v>
       </c>
@@ -7159,7 +7149,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>335</v>
       </c>
@@ -7193,7 +7183,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>115</v>
       </c>
@@ -7227,7 +7217,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>401</v>
       </c>
@@ -7261,7 +7251,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>465</v>
       </c>
@@ -7295,7 +7285,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>279</v>
       </c>
@@ -7329,7 +7319,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>483</v>
       </c>
@@ -7363,7 +7353,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -7397,7 +7387,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>153</v>
       </c>
@@ -7431,7 +7421,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>597</v>
       </c>
@@ -7465,7 +7455,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>587</v>
       </c>
@@ -7499,7 +7489,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>631</v>
       </c>
@@ -7533,7 +7523,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>151</v>
       </c>
@@ -7567,7 +7557,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>283</v>
       </c>
@@ -7601,7 +7591,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>369</v>
       </c>
@@ -7635,7 +7625,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>507</v>
       </c>
@@ -7669,7 +7659,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>161</v>
       </c>
@@ -7703,7 +7693,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>227</v>
       </c>
@@ -7737,7 +7727,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>843</v>
       </c>
@@ -7771,7 +7761,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>553</v>
       </c>
@@ -7805,7 +7795,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>573</v>
       </c>
@@ -7839,7 +7829,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>331</v>
       </c>
@@ -7873,7 +7863,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>453</v>
       </c>
@@ -7907,7 +7897,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>525</v>
       </c>
@@ -7941,7 +7931,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>851</v>
       </c>
@@ -7975,7 +7965,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>707</v>
       </c>
@@ -8009,7 +7999,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>647</v>
       </c>
@@ -8043,7 +8033,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -8077,7 +8067,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>583</v>
       </c>
@@ -8111,7 +8101,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>741</v>
       </c>
@@ -8145,7 +8135,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>661</v>
       </c>
@@ -8179,7 +8169,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>93</v>
       </c>
@@ -8213,7 +8203,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>431</v>
       </c>
@@ -8247,7 +8237,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -8281,7 +8271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>809</v>
       </c>
@@ -8315,7 +8305,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>345</v>
       </c>
@@ -8349,7 +8339,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>687</v>
       </c>
@@ -8383,7 +8373,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>797</v>
       </c>
@@ -8417,7 +8407,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>119</v>
       </c>
@@ -8451,7 +8441,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>451</v>
       </c>
@@ -8485,7 +8475,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>545</v>
       </c>
@@ -8519,7 +8509,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>241</v>
       </c>
@@ -8553,7 +8543,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>55</v>
       </c>
@@ -8587,7 +8577,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>721</v>
       </c>
@@ -8621,7 +8611,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>323</v>
       </c>
@@ -8655,7 +8645,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>259</v>
       </c>
@@ -8689,7 +8679,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>807</v>
       </c>
@@ -8723,7 +8713,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>185</v>
       </c>
@@ -8757,7 +8747,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>163</v>
       </c>
@@ -8791,7 +8781,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>415</v>
       </c>
@@ -8825,7 +8815,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>657</v>
       </c>
@@ -8859,7 +8849,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>703</v>
       </c>
@@ -8893,7 +8883,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -8927,7 +8917,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>505</v>
       </c>
@@ -8961,7 +8951,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>589</v>
       </c>
@@ -8995,7 +8985,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>419</v>
       </c>
@@ -9029,7 +9019,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>709</v>
       </c>
@@ -9063,7 +9053,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>787</v>
       </c>
@@ -9097,7 +9087,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -9131,7 +9121,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>319</v>
       </c>
@@ -9165,7 +9155,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>167</v>
       </c>
@@ -9199,7 +9189,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>347</v>
       </c>
@@ -9233,7 +9223,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>561</v>
       </c>
@@ -9267,7 +9257,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>213</v>
       </c>
@@ -9301,7 +9291,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>411</v>
       </c>
@@ -9335,7 +9325,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>759</v>
       </c>
@@ -9369,7 +9359,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>315</v>
       </c>
@@ -9403,7 +9393,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>769</v>
       </c>
@@ -9437,7 +9427,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>677</v>
       </c>
@@ -9471,7 +9461,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>629</v>
       </c>
@@ -9505,7 +9495,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>745</v>
       </c>
@@ -9539,7 +9529,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>187</v>
       </c>
@@ -9573,7 +9563,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>263</v>
       </c>
@@ -9607,7 +9597,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>275</v>
       </c>
@@ -9641,7 +9631,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>239</v>
       </c>
@@ -9675,7 +9665,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>17</v>
       </c>
@@ -9709,7 +9699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>607</v>
       </c>
@@ -9743,7 +9733,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>467</v>
       </c>
@@ -9777,7 +9767,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>801</v>
       </c>
@@ -9811,7 +9801,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>667</v>
       </c>
@@ -9845,7 +9835,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>313</v>
       </c>
@@ -9879,7 +9869,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>719</v>
       </c>
@@ -9913,7 +9903,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>837</v>
       </c>
@@ -9947,7 +9937,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>627</v>
       </c>
@@ -9981,7 +9971,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>749</v>
       </c>
@@ -10015,7 +10005,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>739</v>
       </c>
@@ -10049,7 +10039,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>473</v>
       </c>
@@ -10083,7 +10073,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>105</v>
       </c>
@@ -10117,7 +10107,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>701</v>
       </c>
@@ -10151,7 +10141,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>681</v>
       </c>
@@ -10185,7 +10175,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>247</v>
       </c>
@@ -10219,7 +10209,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>133</v>
       </c>
@@ -10253,7 +10243,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>439</v>
       </c>
@@ -10287,7 +10277,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>191</v>
       </c>
@@ -10321,7 +10311,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>603</v>
       </c>
@@ -10355,7 +10345,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>693</v>
       </c>
@@ -10389,7 +10379,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>77</v>
       </c>
@@ -10423,7 +10413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -10457,7 +10447,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>731</v>
       </c>
@@ -10491,7 +10481,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>841</v>
       </c>
@@ -10525,7 +10515,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>353</v>
       </c>
@@ -10559,7 +10549,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>293</v>
       </c>
@@ -10593,7 +10583,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>513</v>
       </c>
@@ -10627,7 +10617,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>117</v>
       </c>
@@ -10661,7 +10651,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>121</v>
       </c>
@@ -10695,7 +10685,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>521</v>
       </c>
@@ -10729,7 +10719,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>511</v>
       </c>
@@ -10763,7 +10753,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>459</v>
       </c>
@@ -10797,7 +10787,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>567</v>
       </c>
@@ -10831,7 +10821,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>765</v>
       </c>
@@ -10865,7 +10855,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>619</v>
       </c>
@@ -10899,7 +10889,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>789</v>
       </c>
@@ -10933,7 +10923,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>237</v>
       </c>
@@ -10967,7 +10957,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>405</v>
       </c>
@@ -11001,7 +10991,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>645</v>
       </c>
@@ -11035,7 +11025,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>417</v>
       </c>
@@ -11069,7 +11059,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>113</v>
       </c>
@@ -11103,7 +11093,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>61</v>
       </c>
@@ -11137,7 +11127,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>25</v>
       </c>
@@ -11171,7 +11161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>697</v>
       </c>
@@ -11205,7 +11195,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>847</v>
       </c>
@@ -11239,7 +11229,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>69</v>
       </c>
@@ -11273,7 +11263,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>425</v>
       </c>
@@ -11307,7 +11297,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>129</v>
       </c>
@@ -11341,7 +11331,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>785</v>
       </c>
@@ -11375,7 +11365,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>169</v>
       </c>
@@ -11409,7 +11399,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>349</v>
       </c>
@@ -11443,7 +11433,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>367</v>
       </c>
@@ -11477,7 +11467,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>125</v>
       </c>
@@ -11511,7 +11501,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>199</v>
       </c>
@@ -11545,7 +11535,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>503</v>
       </c>
@@ -11579,7 +11569,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>613</v>
       </c>
@@ -11613,7 +11603,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>359</v>
       </c>
@@ -11647,7 +11637,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>63</v>
       </c>
@@ -11681,7 +11671,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>329</v>
       </c>
@@ -11715,7 +11705,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>575</v>
       </c>
@@ -11749,7 +11739,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>499</v>
       </c>
@@ -11783,7 +11773,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>235</v>
       </c>
@@ -11817,7 +11807,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>267</v>
       </c>
@@ -11851,7 +11841,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>381</v>
       </c>
@@ -11885,7 +11875,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>743</v>
       </c>
@@ -11919,7 +11909,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>713</v>
       </c>
@@ -11953,7 +11943,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>653</v>
       </c>
@@ -11987,7 +11977,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>403</v>
       </c>
@@ -12021,7 +12011,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>165</v>
       </c>
@@ -12055,7 +12045,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>229</v>
       </c>
@@ -12089,7 +12079,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>723</v>
       </c>
@@ -12123,7 +12113,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>269</v>
       </c>
@@ -12157,7 +12147,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>635</v>
       </c>
@@ -12191,7 +12181,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>729</v>
       </c>
@@ -12225,7 +12215,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>391</v>
       </c>
@@ -12259,7 +12249,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>535</v>
       </c>
@@ -12293,7 +12283,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>155</v>
       </c>
@@ -12327,7 +12317,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>361</v>
       </c>
@@ -12361,7 +12351,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>717</v>
       </c>
@@ -12395,7 +12385,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>493</v>
       </c>
@@ -12429,7 +12419,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>487</v>
       </c>
@@ -12463,7 +12453,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>137</v>
       </c>
@@ -12497,7 +12487,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>67</v>
       </c>
@@ -12531,7 +12521,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>779</v>
       </c>
@@ -12565,7 +12555,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>449</v>
       </c>
@@ -12599,7 +12589,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>579</v>
       </c>
@@ -12633,7 +12623,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>649</v>
       </c>
@@ -12667,7 +12657,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>783</v>
       </c>
@@ -12701,7 +12691,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>727</v>
       </c>
@@ -12735,7 +12725,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>379</v>
       </c>
@@ -12769,7 +12759,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>23</v>
       </c>
@@ -12803,7 +12793,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>291</v>
       </c>
@@ -12837,7 +12827,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1496</v>
       </c>
@@ -12868,7 +12858,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1498</v>
       </c>
@@ -12899,7 +12889,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1500</v>
       </c>
@@ -12930,7 +12920,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1494</v>
       </c>
@@ -12961,7 +12951,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1354</v>
       </c>
@@ -12992,7 +12982,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1356</v>
       </c>
@@ -13023,7 +13013,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1358</v>
       </c>
@@ -13054,7 +13044,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1360</v>
       </c>
@@ -13085,7 +13075,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1362</v>
       </c>
@@ -13116,7 +13106,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1364</v>
       </c>
@@ -13147,7 +13137,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1366</v>
       </c>
@@ -13178,7 +13168,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1368</v>
       </c>
@@ -13209,7 +13199,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1372</v>
       </c>
@@ -13240,7 +13230,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1370</v>
       </c>
@@ -13271,7 +13261,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1374</v>
       </c>
@@ -13302,7 +13292,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1420</v>
       </c>
@@ -13333,7 +13323,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1422</v>
       </c>
@@ -13364,7 +13354,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1418</v>
       </c>
@@ -13395,7 +13385,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1376</v>
       </c>
@@ -13426,7 +13416,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1378</v>
       </c>
@@ -13457,7 +13447,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1380</v>
       </c>
@@ -13488,7 +13478,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1382</v>
       </c>
@@ -13519,7 +13509,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1384</v>
       </c>
@@ -13550,7 +13540,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>966</v>
       </c>
@@ -13578,7 +13568,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1036</v>
       </c>
@@ -13606,7 +13596,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1386</v>
       </c>
@@ -13637,7 +13627,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1094</v>
       </c>
@@ -13665,7 +13655,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>984</v>
       </c>
@@ -13693,7 +13683,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>907</v>
       </c>
@@ -13721,7 +13711,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1118</v>
       </c>
@@ -13749,7 +13739,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1042</v>
       </c>
@@ -13777,7 +13767,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1232</v>
       </c>
@@ -13805,7 +13795,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1136</v>
       </c>
@@ -13833,7 +13823,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1156</v>
       </c>
@@ -13861,7 +13851,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1264</v>
       </c>
@@ -13889,7 +13879,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>964</v>
       </c>
@@ -13917,7 +13907,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1222</v>
       </c>
@@ -13945,7 +13935,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1308</v>
       </c>
@@ -13970,7 +13960,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>925</v>
       </c>
@@ -13998,7 +13988,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1242</v>
       </c>
@@ -14023,7 +14013,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1228</v>
       </c>
@@ -14051,7 +14041,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1018</v>
       </c>
@@ -14079,7 +14069,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>951</v>
       </c>
@@ -14107,7 +14097,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1268</v>
       </c>
@@ -14135,7 +14125,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1010</v>
       </c>
@@ -14163,7 +14153,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1174</v>
       </c>
@@ -14191,7 +14181,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1278</v>
       </c>
@@ -14219,7 +14209,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1162</v>
       </c>
@@ -14247,7 +14237,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1150</v>
       </c>
@@ -14275,7 +14265,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1002</v>
       </c>
@@ -14303,7 +14293,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>943</v>
       </c>
@@ -14331,7 +14321,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>903</v>
       </c>
@@ -14359,7 +14349,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>889</v>
       </c>
@@ -14387,7 +14377,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1388</v>
       </c>
@@ -14418,7 +14408,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1342</v>
       </c>
@@ -14446,7 +14436,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1344</v>
       </c>
@@ -14474,7 +14464,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1352</v>
       </c>
@@ -14502,7 +14492,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1350</v>
       </c>
@@ -14530,7 +14520,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1338</v>
       </c>
@@ -14558,7 +14548,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1346</v>
       </c>
@@ -14586,7 +14576,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1340</v>
       </c>
@@ -14614,7 +14604,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1334</v>
       </c>
@@ -14642,7 +14632,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1330</v>
       </c>
@@ -14670,7 +14660,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1348</v>
       </c>
@@ -14698,7 +14688,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1336</v>
       </c>
@@ -14726,7 +14716,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1390</v>
       </c>
@@ -14757,7 +14747,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1332</v>
       </c>
@@ -14785,7 +14775,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1392</v>
       </c>
@@ -14816,7 +14806,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1394</v>
       </c>
@@ -14847,7 +14837,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1076</v>
       </c>
@@ -14875,7 +14865,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>927</v>
       </c>
@@ -14903,7 +14893,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>897</v>
       </c>
@@ -14931,7 +14921,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1190</v>
       </c>
@@ -14959,7 +14949,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>996</v>
       </c>
@@ -14987,7 +14977,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>988</v>
       </c>
@@ -15015,7 +15005,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1026</v>
       </c>
@@ -15043,7 +15033,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1188</v>
       </c>
@@ -15071,7 +15061,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>901</v>
       </c>
@@ -15099,7 +15089,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1180</v>
       </c>
@@ -15127,7 +15117,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1210</v>
       </c>
@@ -15155,7 +15145,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1048</v>
       </c>
@@ -15183,7 +15173,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1154</v>
       </c>
@@ -15211,7 +15201,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>968</v>
       </c>
@@ -15239,7 +15229,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>990</v>
       </c>
@@ -15267,7 +15257,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>954</v>
       </c>
@@ -15295,7 +15285,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1032</v>
       </c>
@@ -15323,7 +15313,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1186</v>
       </c>
@@ -15351,7 +15341,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1282</v>
       </c>
@@ -15379,7 +15369,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1248</v>
       </c>
@@ -15407,7 +15397,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>909</v>
       </c>
@@ -15435,7 +15425,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>941</v>
       </c>
@@ -15463,7 +15453,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1028</v>
       </c>
@@ -15491,7 +15481,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1194</v>
       </c>
@@ -15519,7 +15509,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1224</v>
       </c>
@@ -15547,7 +15537,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>974</v>
       </c>
@@ -15575,7 +15565,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>982</v>
       </c>
@@ -15603,7 +15593,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1192</v>
       </c>
@@ -15631,7 +15621,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1040</v>
       </c>
@@ -15659,7 +15649,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1066</v>
       </c>
@@ -15687,7 +15677,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>994</v>
       </c>
@@ -15715,7 +15705,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1034</v>
       </c>
@@ -15743,7 +15733,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1138</v>
       </c>
@@ -15771,7 +15761,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1044</v>
       </c>
@@ -15799,7 +15789,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1244</v>
       </c>
@@ -15827,7 +15817,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1238</v>
       </c>
@@ -15855,7 +15845,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1168</v>
       </c>
@@ -15883,7 +15873,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1142</v>
       </c>
@@ -15911,7 +15901,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1090</v>
       </c>
@@ -15939,7 +15929,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1246</v>
       </c>
@@ -15967,7 +15957,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1276</v>
       </c>
@@ -15995,7 +15985,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1270</v>
       </c>
@@ -16023,7 +16013,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1254</v>
       </c>
@@ -16051,7 +16041,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1062</v>
       </c>
@@ -16079,7 +16069,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1312</v>
       </c>
@@ -16107,7 +16097,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1236</v>
       </c>
@@ -16135,7 +16125,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>905</v>
       </c>
@@ -16177,7 +16167,7 @@
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1320</v>
       </c>
@@ -16205,7 +16195,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>893</v>
       </c>
@@ -16233,7 +16223,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1198</v>
       </c>
@@ -16261,7 +16251,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1204</v>
       </c>
@@ -16289,7 +16279,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1080</v>
       </c>
@@ -16317,7 +16307,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1070</v>
       </c>
@@ -16345,7 +16335,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1298</v>
       </c>
@@ -16373,7 +16363,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1016</v>
       </c>
@@ -16401,7 +16391,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>923</v>
       </c>
@@ -16429,7 +16419,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1284</v>
       </c>
@@ -16457,7 +16447,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1226</v>
       </c>
@@ -16485,7 +16475,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1132</v>
       </c>
@@ -16513,7 +16503,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1252</v>
       </c>
@@ -16541,7 +16531,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>915</v>
       </c>
@@ -16569,7 +16559,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1318</v>
       </c>
@@ -16597,7 +16587,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1058</v>
       </c>
@@ -16625,7 +16615,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>911</v>
       </c>
@@ -16653,7 +16643,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1158</v>
       </c>
@@ -16681,7 +16671,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1172</v>
       </c>
@@ -16709,7 +16699,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1082</v>
       </c>
@@ -16737,7 +16727,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1286</v>
       </c>
@@ -16765,7 +16755,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>895</v>
       </c>
@@ -16793,7 +16783,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1054</v>
       </c>
@@ -16821,7 +16811,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1300</v>
       </c>
@@ -16849,7 +16839,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1114</v>
       </c>
@@ -16877,7 +16867,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1314</v>
       </c>
@@ -16905,7 +16895,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>945</v>
       </c>
@@ -16933,7 +16923,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1296</v>
       </c>
@@ -16961,7 +16951,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>917</v>
       </c>
@@ -16989,7 +16979,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1220</v>
       </c>
@@ -17017,7 +17007,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="364" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1124</v>
       </c>
@@ -17045,7 +17035,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="365" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1012</v>
       </c>
@@ -17073,7 +17063,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>891</v>
       </c>
@@ -17101,7 +17091,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="367" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1140</v>
       </c>
@@ -17129,7 +17119,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="368" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>937</v>
       </c>
@@ -17157,7 +17147,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1266</v>
       </c>
@@ -17185,7 +17175,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>960</v>
       </c>
@@ -17213,7 +17203,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>972</v>
       </c>
@@ -17241,7 +17231,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1304</v>
       </c>
@@ -17269,7 +17259,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1206</v>
       </c>
@@ -17297,7 +17287,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1064</v>
       </c>
@@ -17325,7 +17315,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1208</v>
       </c>
@@ -17353,7 +17343,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>958</v>
       </c>
@@ -17381,7 +17371,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1292</v>
       </c>
@@ -17409,7 +17399,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1324</v>
       </c>
@@ -17437,7 +17427,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>921</v>
       </c>
@@ -17465,7 +17455,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1272</v>
       </c>
@@ -17493,7 +17483,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="381" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1288</v>
       </c>
@@ -17521,7 +17511,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="382" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1092</v>
       </c>
@@ -17549,7 +17539,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>947</v>
       </c>
@@ -17577,7 +17567,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1098</v>
       </c>
@@ -17605,7 +17595,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1128</v>
       </c>
@@ -17633,7 +17623,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>899</v>
       </c>
@@ -17661,7 +17651,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1326</v>
       </c>
@@ -17689,7 +17679,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1052</v>
       </c>
@@ -17717,7 +17707,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="389" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1328</v>
       </c>
@@ -17745,7 +17735,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1184</v>
       </c>
@@ -17773,7 +17763,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1004</v>
       </c>
@@ -17801,7 +17791,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="392" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>992</v>
       </c>
@@ -17829,7 +17819,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>998</v>
       </c>
@@ -17857,7 +17847,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1122</v>
       </c>
@@ -17885,7 +17875,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="395" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1182</v>
       </c>
@@ -17913,7 +17903,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="396" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1046</v>
       </c>
@@ -17941,7 +17931,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="397" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1164</v>
       </c>
@@ -17969,7 +17959,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="398" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1280</v>
       </c>
@@ -17997,7 +17987,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="399" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1056</v>
       </c>
@@ -18025,7 +18015,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="400" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>931</v>
       </c>
@@ -18053,7 +18043,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="401" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>980</v>
       </c>
@@ -18081,7 +18071,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="402" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1130</v>
       </c>
@@ -18109,7 +18099,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="403" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>956</v>
       </c>
@@ -18137,7 +18127,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="404" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1084</v>
       </c>
@@ -18165,7 +18155,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="405" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1230</v>
       </c>
@@ -18193,7 +18183,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="406" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1108</v>
       </c>
@@ -18221,7 +18211,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="407" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1170</v>
       </c>
@@ -18249,7 +18239,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="408" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1074</v>
       </c>
@@ -18277,7 +18267,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="409" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1102</v>
       </c>
@@ -18305,7 +18295,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="410" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1262</v>
       </c>
@@ -18333,7 +18323,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="411" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1110</v>
       </c>
@@ -18361,7 +18351,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="412" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>933</v>
       </c>
@@ -18389,7 +18379,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="413" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1106</v>
       </c>
@@ -18417,7 +18407,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="414" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1144</v>
       </c>
@@ -18445,7 +18435,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="415" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1148</v>
       </c>
@@ -18473,7 +18463,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="416" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1024</v>
       </c>
@@ -18501,7 +18491,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="417" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1008</v>
       </c>
@@ -18529,7 +18519,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="418" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>929</v>
       </c>
@@ -18557,7 +18547,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="419" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1104</v>
       </c>
@@ -18585,7 +18575,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="420" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1126</v>
       </c>
@@ -18613,7 +18603,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="421" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1006</v>
       </c>
@@ -18641,7 +18631,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="422" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1000</v>
       </c>
@@ -18669,7 +18659,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="423" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1020</v>
       </c>
@@ -18697,7 +18687,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="424" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>919</v>
       </c>
@@ -18725,7 +18715,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="425" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1078</v>
       </c>
@@ -18753,7 +18743,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="426" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1100</v>
       </c>
@@ -18781,7 +18771,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="427" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1088</v>
       </c>
@@ -18809,7 +18799,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="428" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>962</v>
       </c>
@@ -18837,7 +18827,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="429" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1060</v>
       </c>
@@ -18865,7 +18855,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="430" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>913</v>
       </c>
@@ -18893,7 +18883,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="431" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1176</v>
       </c>
@@ -18921,7 +18911,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="432" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1134</v>
       </c>
@@ -18949,7 +18939,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="433" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1030</v>
       </c>
@@ -18977,7 +18967,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="434" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1146</v>
       </c>
@@ -19005,7 +18995,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="435" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1258</v>
       </c>
@@ -19033,7 +19023,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="436" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>986</v>
       </c>
@@ -19061,7 +19051,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="437" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>939</v>
       </c>
@@ -19089,7 +19079,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="438" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1274</v>
       </c>
@@ -19117,7 +19107,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="439" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1250</v>
       </c>
@@ -19145,7 +19135,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="440" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>949</v>
       </c>
@@ -19173,7 +19163,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="441" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1306</v>
       </c>
@@ -19201,7 +19191,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="442" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1116</v>
       </c>
@@ -19229,7 +19219,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="443" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1256</v>
       </c>
@@ -19257,7 +19247,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="444" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1068</v>
       </c>
@@ -19285,7 +19275,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="445" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1316</v>
       </c>
@@ -19313,7 +19303,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="446" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1050</v>
       </c>
@@ -19341,7 +19331,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="447" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1196</v>
       </c>
@@ -19369,7 +19359,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="448" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1120</v>
       </c>
@@ -19397,7 +19387,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="449" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>976</v>
       </c>
@@ -19425,7 +19415,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="450" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1166</v>
       </c>
@@ -19453,7 +19443,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="451" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1014</v>
       </c>
@@ -19481,7 +19471,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="452" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1072</v>
       </c>
@@ -19509,7 +19499,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="453" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1112</v>
       </c>
@@ -19537,7 +19527,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="454" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1086</v>
       </c>
@@ -19565,7 +19555,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="455" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1200</v>
       </c>
@@ -19593,7 +19583,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="456" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1152</v>
       </c>
@@ -19621,7 +19611,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="457" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1218</v>
       </c>
@@ -19649,7 +19639,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="458" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1216</v>
       </c>
@@ -19677,7 +19667,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="459" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>978</v>
       </c>
@@ -19705,7 +19695,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="460" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>935</v>
       </c>
@@ -19733,7 +19723,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="461" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1234</v>
       </c>
@@ -19761,7 +19751,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="462" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1022</v>
       </c>
@@ -19789,7 +19779,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="463" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1202</v>
       </c>
@@ -19817,7 +19807,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="464" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1260</v>
       </c>
@@ -19845,7 +19835,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1038</v>
       </c>
@@ -19873,7 +19863,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>970</v>
       </c>
@@ -19901,7 +19891,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1096</v>
       </c>
@@ -19929,7 +19919,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1240</v>
       </c>
@@ -19957,7 +19947,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1290</v>
       </c>
@@ -19985,7 +19975,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1178</v>
       </c>
@@ -20013,7 +20003,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1310</v>
       </c>
@@ -20041,7 +20031,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1396</v>
       </c>
@@ -20072,7 +20062,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1214</v>
       </c>
@@ -20100,7 +20090,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1294</v>
       </c>
@@ -20128,7 +20118,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1302</v>
       </c>
@@ -20156,7 +20146,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1160</v>
       </c>
@@ -20184,7 +20174,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1212</v>
       </c>
@@ -20212,7 +20202,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1322</v>
       </c>
@@ -20240,7 +20230,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1398</v>
       </c>
@@ -20271,7 +20261,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1400</v>
       </c>
@@ -20302,7 +20292,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1402</v>
       </c>
@@ -20333,7 +20323,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1404</v>
       </c>
@@ -20364,7 +20354,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1406</v>
       </c>
@@ -20395,7 +20385,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1408</v>
       </c>
@@ -20426,7 +20416,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1410</v>
       </c>
@@ -20457,7 +20447,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1412</v>
       </c>
@@ -20488,7 +20478,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1414</v>
       </c>
@@ -20519,7 +20509,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1416</v>
       </c>
@@ -20550,7 +20540,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1424</v>
       </c>
@@ -20584,7 +20574,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1426</v>
       </c>
@@ -20618,7 +20608,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1428</v>
       </c>
@@ -20652,7 +20642,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1430</v>
       </c>
@@ -20686,7 +20676,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1432</v>
       </c>
@@ -20720,7 +20710,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1434</v>
       </c>
@@ -20754,7 +20744,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1436</v>
       </c>
@@ -20788,7 +20778,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1438</v>
       </c>
@@ -20822,7 +20812,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1442</v>
       </c>
@@ -20856,7 +20846,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1440</v>
       </c>
@@ -20890,7 +20880,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1444</v>
       </c>
@@ -20924,7 +20914,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1448</v>
       </c>
@@ -20958,7 +20948,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1450</v>
       </c>
@@ -20992,7 +20982,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1446</v>
       </c>
@@ -21026,7 +21016,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1452</v>
       </c>
@@ -21060,7 +21050,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1454</v>
       </c>
@@ -21094,7 +21084,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1456</v>
       </c>
@@ -21128,7 +21118,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1458</v>
       </c>
@@ -21162,7 +21152,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1460</v>
       </c>
@@ -21196,7 +21186,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>599</v>
       </c>
@@ -21227,7 +21217,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>671</v>
       </c>
@@ -21258,7 +21248,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1462</v>
       </c>
@@ -21292,7 +21282,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>289</v>
       </c>
@@ -21323,7 +21313,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>691</v>
       </c>
@@ -21354,7 +21344,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="513" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>577</v>
       </c>
@@ -21385,7 +21375,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="514" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>95</v>
       </c>
@@ -21416,7 +21406,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="515" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>393</v>
       </c>
@@ -21447,7 +21437,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="516" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>515</v>
       </c>
@@ -21478,7 +21468,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="517" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>517</v>
       </c>
@@ -21509,7 +21499,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="518" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>149</v>
       </c>
@@ -21540,7 +21530,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="519" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>65</v>
       </c>
@@ -21571,7 +21561,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="520" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>301</v>
       </c>
@@ -21602,7 +21592,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="521" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>437</v>
       </c>
@@ -21633,7 +21623,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="522" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>253</v>
       </c>
@@ -21661,7 +21651,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="523" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>317</v>
       </c>
@@ -21692,7 +21682,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="524" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>685</v>
       </c>
@@ -21720,7 +21710,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="525" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>341</v>
       </c>
@@ -21751,7 +21741,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="526" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>471</v>
       </c>
@@ -21782,7 +21772,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="527" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>209</v>
       </c>
@@ -21813,7 +21803,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="528" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>177</v>
       </c>
@@ -21844,7 +21834,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>87</v>
       </c>
@@ -21875,7 +21865,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1464</v>
       </c>
@@ -21909,7 +21899,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>857</v>
       </c>
@@ -21940,7 +21930,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>881</v>
       </c>
@@ -21971,7 +21961,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>887</v>
       </c>
@@ -22002,7 +21992,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>859</v>
       </c>
@@ -22033,7 +22023,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>873</v>
       </c>
@@ -22064,7 +22054,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>875</v>
       </c>
@@ -22095,7 +22085,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>885</v>
       </c>
@@ -22126,7 +22116,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>863</v>
       </c>
@@ -22157,7 +22147,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>879</v>
       </c>
@@ -22188,7 +22178,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>869</v>
       </c>
@@ -22219,7 +22209,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1466</v>
       </c>
@@ -22253,7 +22243,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>871</v>
       </c>
@@ -22284,7 +22274,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1468</v>
       </c>
@@ -22318,7 +22308,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1470</v>
       </c>
@@ -22352,7 +22342,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="545" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>773</v>
       </c>
@@ -22383,7 +22373,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="546" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>763</v>
       </c>
@@ -22414,7 +22404,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="547" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>413</v>
       </c>
@@ -22445,7 +22435,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="548" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>85</v>
       </c>
@@ -22476,7 +22466,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="549" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>527</v>
       </c>
@@ -22507,7 +22497,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="550" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>805</v>
       </c>
@@ -22538,7 +22528,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="551" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>173</v>
       </c>
@@ -22569,7 +22559,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="552" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>255</v>
       </c>
@@ -22600,7 +22590,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="553" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>73</v>
       </c>
@@ -22631,7 +22621,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="554" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>321</v>
       </c>
@@ -22662,7 +22652,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="555" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>601</v>
       </c>
@@ -22693,7 +22683,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="556" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>585</v>
       </c>
@@ -22724,7 +22714,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="557" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>193</v>
       </c>
@@ -22755,7 +22745,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="558" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>243</v>
       </c>
@@ -22786,7 +22776,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="559" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>143</v>
       </c>
@@ -22817,7 +22807,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="560" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>799</v>
       </c>
@@ -22848,7 +22838,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="561" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>327</v>
       </c>
@@ -22879,7 +22869,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="562" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>821</v>
       </c>
@@ -22910,7 +22900,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="563" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>427</v>
       </c>
@@ -22941,7 +22931,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="564" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>231</v>
       </c>
@@ -22972,7 +22962,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="565" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>433</v>
       </c>
@@ -23003,7 +22993,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="566" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>407</v>
       </c>
@@ -23034,7 +23024,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="567" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>287</v>
       </c>
@@ -23065,7 +23055,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="568" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>593</v>
       </c>
@@ -23096,7 +23086,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="569" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>47</v>
       </c>
@@ -23127,7 +23117,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="570" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>357</v>
       </c>
@@ -23158,7 +23148,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="571" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>223</v>
       </c>
@@ -23189,7 +23179,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="572" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>371</v>
       </c>
@@ -23220,7 +23210,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="573" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>265</v>
       </c>
@@ -23251,7 +23241,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="574" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>699</v>
       </c>
@@ -23282,7 +23272,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="575" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>27</v>
       </c>
@@ -23313,7 +23303,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="576" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>735</v>
       </c>
@@ -23344,7 +23334,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="577" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>477</v>
       </c>
@@ -23375,7 +23365,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="578" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>373</v>
       </c>
@@ -23406,7 +23396,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="579" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>245</v>
       </c>
@@ -23437,7 +23427,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="580" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>219</v>
       </c>
@@ -23468,7 +23458,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="581" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>399</v>
       </c>
@@ -23499,7 +23489,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="582" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>297</v>
       </c>
@@ -23530,7 +23520,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="583" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>737</v>
       </c>
@@ -23561,7 +23551,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="584" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>795</v>
       </c>
@@ -23592,7 +23582,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="585" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>295</v>
       </c>
@@ -23623,7 +23613,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="586" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>551</v>
       </c>
@@ -23654,7 +23644,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="587" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>131</v>
       </c>
@@ -23685,7 +23675,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="588" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>307</v>
       </c>
@@ -23716,7 +23706,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="589" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>747</v>
       </c>
@@ -23747,7 +23737,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="590" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>29</v>
       </c>
@@ -23778,7 +23768,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="591" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>123</v>
       </c>
@@ -23809,7 +23799,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="592" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>623</v>
       </c>
@@ -23840,7 +23830,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="593" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>615</v>
       </c>
@@ -23871,7 +23861,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="594" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>695</v>
       </c>
@@ -23902,7 +23892,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="595" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>71</v>
       </c>
@@ -23933,7 +23923,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="596" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>421</v>
       </c>
@@ -23964,7 +23954,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="597" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>183</v>
       </c>
@@ -23995,7 +23985,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="598" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>815</v>
       </c>
@@ -24026,7 +24016,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="599" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>305</v>
       </c>
@@ -24057,7 +24047,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="600" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>101</v>
       </c>
@@ -24088,7 +24078,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="601" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>849</v>
       </c>
@@ -24119,7 +24109,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="602" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>571</v>
       </c>
@@ -24150,7 +24140,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="603" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>663</v>
       </c>
@@ -24181,7 +24171,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="604" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>609</v>
       </c>
@@ -24212,7 +24202,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="605" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>509</v>
       </c>
@@ -24243,7 +24233,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="606" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>445</v>
       </c>
@@ -24274,7 +24264,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="607" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>233</v>
       </c>
@@ -24305,7 +24295,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="608" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>103</v>
       </c>
@@ -24336,7 +24326,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="609" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>447</v>
       </c>
@@ -24367,7 +24357,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="610" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>537</v>
       </c>
@@ -24398,7 +24388,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="611" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>355</v>
       </c>
@@ -24429,7 +24419,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="612" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>389</v>
       </c>
@@ -24460,7 +24450,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="613" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>249</v>
       </c>
@@ -24491,7 +24481,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="614" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>409</v>
       </c>
@@ -24522,7 +24512,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="615" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>813</v>
       </c>
@@ -24553,7 +24543,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="616" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>435</v>
       </c>
@@ -24584,7 +24574,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="617" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>203</v>
       </c>
@@ -24615,7 +24605,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="618" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>817</v>
       </c>
@@ -24646,7 +24636,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="619" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>771</v>
       </c>
@@ -24677,7 +24667,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="620" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>547</v>
       </c>
@@ -24708,7 +24698,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="621" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>333</v>
       </c>
@@ -24739,7 +24729,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="622" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>563</v>
       </c>
@@ -24770,7 +24760,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="623" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>251</v>
       </c>
@@ -24801,7 +24791,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="624" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>495</v>
       </c>
@@ -24832,7 +24822,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="625" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>549</v>
       </c>
@@ -24863,7 +24853,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="626" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>595</v>
       </c>
@@ -24894,7 +24884,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="627" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>147</v>
       </c>
@@ -24925,7 +24915,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="628" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>529</v>
       </c>
@@ -24956,7 +24946,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="629" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>665</v>
       </c>
@@ -24987,7 +24977,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="630" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>605</v>
       </c>
@@ -25018,7 +25008,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="631" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>325</v>
       </c>
@@ -25049,7 +25039,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="632" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>19</v>
       </c>
@@ -25080,7 +25070,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="633" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>469</v>
       </c>
@@ -25111,7 +25101,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="634" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>39</v>
       </c>
@@ -25142,7 +25132,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="635" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>811</v>
       </c>
@@ -25173,7 +25163,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="636" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>581</v>
       </c>
@@ -25204,7 +25194,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="637" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>625</v>
       </c>
@@ -25235,7 +25225,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="638" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>833</v>
       </c>
@@ -25266,7 +25256,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="639" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>395</v>
       </c>
@@ -25297,7 +25287,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="640" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>127</v>
       </c>
@@ -25328,7 +25318,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="641" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>753</v>
       </c>
@@ -25359,7 +25349,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="642" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>651</v>
       </c>
@@ -25390,7 +25380,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="643" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>683</v>
       </c>
@@ -25421,7 +25411,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="644" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>261</v>
       </c>
@@ -25452,7 +25442,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="645" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>825</v>
       </c>
@@ -25483,7 +25473,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="646" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>145</v>
       </c>
@@ -25514,7 +25504,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="647" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>781</v>
       </c>
@@ -25545,7 +25535,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="648" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>659</v>
       </c>
@@ -25576,7 +25566,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="649" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>49</v>
       </c>
@@ -25607,7 +25597,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="650" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>79</v>
       </c>
@@ -25638,7 +25628,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="651" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>481</v>
       </c>
@@ -25669,7 +25659,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="652" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>205</v>
       </c>
@@ -25700,7 +25690,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="653" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>33</v>
       </c>
@@ -25731,7 +25721,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="654" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>569</v>
       </c>
@@ -25762,7 +25752,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="655" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>11</v>
       </c>
@@ -25793,7 +25783,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="656" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>159</v>
       </c>
@@ -25824,7 +25814,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="657" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>35</v>
       </c>
@@ -25855,7 +25845,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="658" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>555</v>
       </c>
@@ -25886,7 +25876,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="659" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>339</v>
       </c>
@@ -25917,7 +25907,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="660" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>139</v>
       </c>
@@ -25948,7 +25938,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="661" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>179</v>
       </c>
@@ -25979,7 +25969,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="662" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>89</v>
       </c>
@@ -26010,7 +26000,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="663" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>489</v>
       </c>
@@ -26041,7 +26031,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="664" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>387</v>
       </c>
@@ -26072,7 +26062,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="665" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>793</v>
       </c>
@@ -26103,7 +26093,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="666" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>679</v>
       </c>
@@ -26134,7 +26124,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="667" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>803</v>
       </c>
@@ -26165,7 +26155,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="668" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>299</v>
       </c>
@@ -26196,7 +26186,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="669" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>533</v>
       </c>
@@ -26227,7 +26217,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="670" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>197</v>
       </c>
@@ -26258,7 +26248,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="671" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>221</v>
       </c>
@@ -26289,7 +26279,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="672" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>757</v>
       </c>
@@ -26320,7 +26310,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="673" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>501</v>
       </c>
@@ -26351,7 +26341,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="674" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>755</v>
       </c>
@@ -26382,7 +26372,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="675" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>171</v>
       </c>
@@ -26413,7 +26403,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="676" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>461</v>
       </c>
@@ -26444,7 +26434,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="677" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>83</v>
       </c>
@@ -26475,7 +26465,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="678" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>75</v>
       </c>
@@ -26506,7 +26496,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="679" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>633</v>
       </c>
@@ -26537,7 +26527,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="680" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>443</v>
       </c>
@@ -26568,7 +26558,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="681" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>281</v>
       </c>
@@ -26599,7 +26589,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="682" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>519</v>
       </c>
@@ -26630,7 +26620,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="683" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>257</v>
       </c>
@@ -26661,7 +26651,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="684" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>181</v>
       </c>
@@ -26692,7 +26682,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="685" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>775</v>
       </c>
@@ -26723,7 +26713,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="686" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>491</v>
       </c>
@@ -26754,7 +26744,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="687" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>715</v>
       </c>
@@ -26785,7 +26775,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="688" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>109</v>
       </c>
@@ -26816,7 +26806,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="689" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>675</v>
       </c>
@@ -26847,7 +26837,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="690" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>733</v>
       </c>
@@ -26878,7 +26868,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="691" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>711</v>
       </c>
@@ -26909,7 +26899,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="692" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>455</v>
       </c>
@@ -26940,7 +26930,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="693" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>15</v>
       </c>
@@ -26971,7 +26961,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="694" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>751</v>
       </c>
@@ -27002,7 +26992,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="695" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>225</v>
       </c>
@@ -27033,7 +27023,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="696" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>271</v>
       </c>
@@ -27064,7 +27054,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="697" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>383</v>
       </c>
@@ -27095,7 +27085,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="698" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>705</v>
       </c>
@@ -27126,7 +27116,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="699" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>97</v>
       </c>
@@ -27157,7 +27147,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="700" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>559</v>
       </c>
@@ -27188,7 +27178,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="701" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>725</v>
       </c>
@@ -27219,7 +27209,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="702" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>211</v>
       </c>
@@ -27250,7 +27240,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="703" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>195</v>
       </c>
@@ -27281,7 +27271,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="704" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>141</v>
       </c>
@@ -27312,7 +27302,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="705" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>429</v>
       </c>
@@ -27343,7 +27333,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="706" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>845</v>
       </c>
@@ -27374,7 +27364,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="707" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>497</v>
       </c>
@@ -27405,7 +27395,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="708" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>839</v>
       </c>
@@ -27436,7 +27426,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="709" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>397</v>
       </c>
@@ -27467,7 +27457,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="710" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>463</v>
       </c>
@@ -27498,7 +27488,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="711" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>351</v>
       </c>
@@ -27529,7 +27519,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="712" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>557</v>
       </c>
@@ -27560,7 +27550,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="713" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>823</v>
       </c>
@@ -27591,7 +27581,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="714" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>673</v>
       </c>
@@ -27622,7 +27612,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="715" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>273</v>
       </c>
@@ -27653,7 +27643,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="716" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>655</v>
       </c>
@@ -27684,7 +27674,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="717" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>621</v>
       </c>
@@ -27715,7 +27705,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="718" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>59</v>
       </c>
@@ -27746,7 +27736,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="719" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>641</v>
       </c>
@@ -27777,7 +27767,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="720" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>363</v>
       </c>
@@ -27808,7 +27798,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="721" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>523</v>
       </c>
@@ -27839,7 +27829,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="722" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>591</v>
       </c>
@@ -27870,7 +27860,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="723" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>337</v>
       </c>
@@ -27901,7 +27891,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="724" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>479</v>
       </c>
@@ -27932,7 +27922,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="725" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>457</v>
       </c>
@@ -27963,7 +27953,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="726" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>761</v>
       </c>
@@ -27994,7 +27984,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="727" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>531</v>
       </c>
@@ -28025,7 +28015,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="728" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>277</v>
       </c>
@@ -28056,7 +28046,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="729" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>777</v>
       </c>
@@ -28097,7 +28087,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="731" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>1472</v>
       </c>
@@ -28131,7 +28121,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="732" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>51</v>
       </c>
@@ -28162,7 +28152,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="733" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>611</v>
       </c>
@@ -28193,7 +28183,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="734" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>57</v>
       </c>
@@ -28224,7 +28214,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="735" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>41</v>
       </c>
@@ -28255,7 +28245,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="736" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>617</v>
       </c>
@@ -28286,7 +28276,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="737" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>43</v>
       </c>
@@ -28317,7 +28307,7 @@
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="738" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>1474</v>
       </c>
@@ -28351,7 +28341,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="739" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>1476</v>
       </c>
@@ -28385,7 +28375,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="740" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>1478</v>
       </c>
@@ -28419,7 +28409,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="741" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>1480</v>
       </c>
@@ -28453,7 +28443,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="742" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>1482</v>
       </c>
@@ -28487,7 +28477,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="743" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>1484</v>
       </c>
@@ -28521,7 +28511,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="744" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>1486</v>
       </c>
@@ -28555,7 +28545,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="745" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>1488</v>
       </c>
@@ -28589,7 +28579,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="746" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>1490</v>
       </c>
@@ -28623,7 +28613,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="747" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>1492</v>
       </c>
@@ -28653,7 +28643,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="748" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F748" s="1"/>
       <c r="R748" t="str">
         <f>IF(F748='symbolen-concept-5.1'!S747, "Gelijk", "Niet gelijk")</f>
@@ -28663,7 +28653,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="749" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F749" s="1"/>
       <c r="R749" t="str">
         <f>IF(F749='symbolen-concept-5.1'!S748, "Gelijk", "Niet gelijk")</f>
@@ -28673,603 +28663,284 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="750" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F750" s="1"/>
       <c r="R750" t="str">
         <f>IF(F750='symbolen-concept-5.1'!S749, "Gelijk", "Niet gelijk")</f>
         <v>Niet gelijk</v>
       </c>
     </row>
-    <row r="751" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R751" t="str">
         <f>IF(F751='symbolen-concept-5.1'!S750, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="752" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R752" t="str">
         <f>IF(F752='symbolen-concept-5.1'!S751, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="753" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R753" t="str">
         <f>IF(F753='symbolen-concept-5.1'!S752, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="754" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R754" t="str">
         <f>IF(F754='symbolen-concept-5.1'!S753, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="755" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R755" t="str">
         <f>IF(F755='symbolen-concept-5.1'!S754, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="756" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R756" t="str">
         <f>IF(F756='symbolen-concept-5.1'!S755, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="757" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R757" t="str">
         <f>IF(F757='symbolen-concept-5.1'!S756, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="758" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R758" t="str">
         <f>IF(F758='symbolen-concept-5.1'!S764, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="759" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R759" t="str">
         <f>IF(F759='symbolen-concept-5.1'!S758, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="760" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R760" t="str">
         <f>IF(F760='symbolen-concept-5.1'!S759, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="761" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R761" t="str">
         <f>IF(F761='symbolen-concept-5.1'!S760, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="762" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R762" t="str">
         <f>IF(F762='symbolen-concept-5.1'!S761, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="763" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R763" t="str">
         <f>IF(F763='symbolen-concept-5.1'!S762, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="764" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R764" t="str">
         <f>IF(F764='symbolen-concept-5.1'!S763, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="765" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R765" t="str">
         <f>IF(F765='symbolen-concept-5.1'!S764, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="766" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R766" t="str">
         <f>IF(F766='symbolen-concept-5.1'!S765, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="767" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R767" t="str">
         <f>IF(F767='symbolen-concept-5.1'!S766, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="768" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R768" t="str">
         <f>IF(F768='symbolen-concept-5.1'!S767, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="769" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R769" t="str">
         <f>IF(F769='symbolen-concept-5.1'!S768, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="770" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R770" t="str">
         <f>IF(F770='symbolen-concept-5.1'!S769, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="771" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R771" t="str">
         <f>IF(F771='symbolen-concept-5.1'!S770, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="772" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R772" t="str">
         <f>IF(F772='symbolen-concept-5.1'!S771, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="773" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R773" t="str">
         <f>IF(F773='symbolen-concept-5.1'!S772, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="774" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R774" t="str">
         <f>IF(F774='symbolen-concept-5.1'!S773, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="775" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R775" t="str">
         <f>IF(F775='symbolen-concept-5.1'!S774, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="776" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R776" t="str">
         <f>IF(F776='symbolen-concept-5.1'!S775, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="777" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R777" t="str">
         <f>IF(F777='symbolen-concept-5.1'!S776, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="778" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R778" t="str">
         <f>IF(F778='symbolen-concept-5.1'!S777, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="779" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R779" t="str">
         <f>IF(F779='symbolen-concept-5.1'!S778, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="780" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R780" t="str">
         <f>IF(F780='symbolen-concept-5.1'!S779, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="781" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R781" t="str">
         <f>IF(F781='symbolen-concept-5.1'!S780, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="782" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R782" t="str">
         <f>IF(F782='symbolen-concept-5.1'!S781, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="783" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R783" t="str">
         <f>IF(F783='symbolen-concept-5.1'!S782, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="784" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R784" t="str">
         <f>IF(F784='symbolen-concept-5.1'!S783, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="785" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R785" t="str">
         <f>IF(F785='symbolen-concept-5.1'!S784, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="786" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R786" t="str">
         <f>IF(F786='symbolen-concept-5.1'!S785, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="787" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R787" t="str">
         <f>IF(F787='symbolen-concept-5.1'!S786, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="788" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R788" t="str">
         <f>IF(F788='symbolen-concept-5.1'!S787, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="789" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R789" t="str">
         <f>IF(F789='symbolen-concept-5.1'!S788, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="790" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R790" t="str">
         <f>IF(F790='symbolen-concept-5.1'!S789, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="791" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R791" t="str">
         <f>IF(F791='symbolen-concept-5.1'!S790, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="792" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R792" t="str">
         <f>IF(F792='symbolen-concept-5.1'!S791, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="793" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R793" t="str">
         <f>IF(F793='symbolen-concept-5.1'!S792, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="794" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R794" t="str">
         <f>IF(F794='symbolen-concept-5.1'!S793, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="795" spans="18:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R795" t="str">
         <f>IF(F795='symbolen-concept-5.1'!S794, "Gelijk", "Niet gelijk")</f>
         <v>Gelijk</v>
       </c>
     </row>
-    <row r="796" spans="18:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="797" spans="18:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="798" spans="18:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="799" spans="18:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="800" spans="18:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="801" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="802" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="803" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="804" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="805" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="806" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="807" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="808" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="809" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="810" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="811" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="812" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="813" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="814" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="815" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="816" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="817" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="818" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="819" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="820" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="821" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="822" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="823" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="824" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="825" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="826" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="827" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="828" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="829" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="830" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="831" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="832" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="833" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="834" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="835" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="836" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="837" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="838" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="839" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="840" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="841" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="842" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="843" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="844" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="845" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="846" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="847" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="848" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="849" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="850" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="851" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="852" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="853" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="854" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="855" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="856" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="857" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="858" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="859" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="860" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="861" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="862" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="863" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="864" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="865" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="866" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="867" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="868" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="869" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="870" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="871" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="872" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="873" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="874" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="875" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="876" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="877" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="878" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="879" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="880" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="881" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="882" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="883" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="884" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="885" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="886" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="887" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="888" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="889" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="890" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="891" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="892" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="893" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="894" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="895" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="896" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="897" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="898" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="899" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="900" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="901" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="902" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="903" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="904" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="905" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="906" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="907" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="908" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="909" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="910" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="911" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="912" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="913" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="914" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="915" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="916" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="917" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="918" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="919" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="920" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="921" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="922" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="923" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="924" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="925" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="926" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="927" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="928" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="929" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="930" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="931" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="932" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="933" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="934" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="935" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="936" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="937" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="938" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="939" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="940" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="941" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="942" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="943" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="944" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="945" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="946" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="947" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="948" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="949" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="950" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="951" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="952" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="953" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="954" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="955" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="956" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="957" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="958" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="959" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="960" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="961" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="962" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="963" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="964" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="965" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="966" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="967" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="968" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="969" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="970" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="971" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="972" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="973" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="974" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="975" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="976" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="977" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="978" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="979" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="980" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="981" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="982" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="983" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="984" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="985" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="986" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="987" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="988" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="989" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="990" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="991" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="992" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="993" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="994" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="995" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="996" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="997" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="998" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="999" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1005" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1006" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1007" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1008" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1009" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1010" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1011" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1012" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1013" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1014" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1015" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1016" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1017" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1018" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1019" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1020" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1021" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1022" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1023" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1024" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1025" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1026" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1027" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1028" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1029" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1030" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1031" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1032" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1033" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1034" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1035" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1036" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1037" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1038" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1039" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1040" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1041" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1042" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1043" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1044" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1045" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1046" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1047" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1048" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1049" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1050" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1051" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1052" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1053" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1054" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1055" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1056" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1057" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1058" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1059" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1060" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1061" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1062" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1063" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1064" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1065" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1066" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1067" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1068" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1069" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1070" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1071" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1072" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1073" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1074" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1075" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1076" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1077" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1078" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1079" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1080" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1081" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1082" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1083" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1084" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1085" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1086" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1087" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1088" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1089" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1090" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1091" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1092" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1093" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1094" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1095" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1096" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1097" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1098" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1099" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1100" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1101" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1102" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1103" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1104" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1105" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1106" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1107" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1108" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1109" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1110" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1111" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1112" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1113" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1114" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="1115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
         <v>1486</v>
       </c>
@@ -29292,7 +28963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>1488</v>
       </c>
@@ -29315,7 +28986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>1490</v>
       </c>
@@ -29338,7 +29009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
         <v>1492</v>
       </c>
@@ -29362,16 +29033,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1118" xr:uid="{51E2713C-FA2A-4405-8F21-738B3A046828}">
-    <filterColumn colId="5">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="Niet gelijk"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S1118" xr:uid="{51E2713C-FA2A-4405-8F21-738B3A046828}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
